--- a/EXCEL/Figur3_klassificering.xlsx
+++ b/EXCEL/Figur3_klassificering.xlsx
@@ -88,7 +88,7 @@
     <t>Datasæt 02 2020</t>
   </si>
   <si>
-    <t>Kørsel 7.4.2026 11.10.03</t>
+    <t>Kørsel 7.4.2026 11.20.59</t>
   </si>
   <si>
     <t>Undergrænse: 5</t>

--- a/EXCEL/Figur3_klassificering.xlsx
+++ b/EXCEL/Figur3_klassificering.xlsx
@@ -88,7 +88,7 @@
     <t>Datasæt 02 2020</t>
   </si>
   <si>
-    <t>Kørsel 7.4.2026 11.20.59</t>
+    <t>Kørsel 7.4.2026 12.44.44</t>
   </si>
   <si>
     <t>Undergrænse: 5</t>

--- a/EXCEL/Figur3_klassificering.xlsx
+++ b/EXCEL/Figur3_klassificering.xlsx
@@ -88,7 +88,7 @@
     <t>Datasæt 02 2020</t>
   </si>
   <si>
-    <t>Kørsel 7.4.2026 12.44.44</t>
+    <t>Kørsel 7.4.2026 12.45.21</t>
   </si>
   <si>
     <t>Undergrænse: 5</t>
